--- a/artfynd/A 26385-2023 artfynd.xlsx
+++ b/artfynd/A 26385-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26385-2023 artfynd.xlsx
+++ b/artfynd/A 26385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80000956</v>
+        <v>56699117</v>
       </c>
       <c r="B2" t="n">
-        <v>57133</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100041</v>
+        <v>131</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Granlundlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Bacidia laurocerasi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Delise ex Duby) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekbacken, Ög</t>
+          <t>Bergsbrant Korpklint, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574245.9331973131</v>
+        <v>574040</v>
       </c>
       <c r="R2" t="n">
-        <v>6505393.860064601</v>
+        <v>6505683</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>Observatör: Mikael Hagström.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,40 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>rasbrant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Håkansson</t>
+          <t>Siri Axelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Ostlänken Norrköpings kommun (OLP2)</t>
-        </is>
-      </c>
+          <t>Via Siri Axelson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97784188</v>
+        <v>80001331</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -855,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574267.5050753297</v>
+        <v>573915</v>
       </c>
       <c r="R3" t="n">
-        <v>6505328.227546699</v>
+        <v>6505667</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,65 +862,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Elin Håkansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Eva Siljeholm</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ostlänken Norrköpings kommun (OLP2)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98350752</v>
+        <v>80001333</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>1460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korpklint, Ög</t>
+          <t>Ekbacken, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573934.5192830344</v>
+        <v>574028</v>
       </c>
       <c r="R4" t="n">
-        <v>6505660.931744166</v>
+        <v>6505493</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +959,1044 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Elin Håkansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ostlänken Norrköpings kommun (OLP2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98350731</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97785</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>573981</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505682</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Marika Sjödin, Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98350752</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573935</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505661</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98350753</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573976</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98350748</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92348</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574037</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505219</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97784194</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574179</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-12-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-12-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>80001311</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574051</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6505688</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-06-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-06-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Håkansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ostlänken Norrköpings kommun (OLP2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97784188</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>574267</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6505328</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-12-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-12-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98350710</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574081</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6505187</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-01-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>80001334</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korpklint, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6505681</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-06-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-06-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Håkansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ostlänken Norrköpings kommun (OLP2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>80000421</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56888</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100041</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Coronella austriaca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ekbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574246</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6505394</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-07-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-07-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>rasbrant</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Håkansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ostlänken Norrköpings kommun (OLP2)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26385-2023 artfynd.xlsx
+++ b/artfynd/A 26385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56699117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Ostlänken Norrköpings kommun (OLP2)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80001331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
           <t>Ostlänken Norrköpings kommun (OLP2)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80001333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98350731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98350752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98350753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98350748</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97784194</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t>Ostlänken Norrköpings kommun (OLP2)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80001311</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97784188</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98350710</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
           <t>Ostlänken Norrköpings kommun (OLP2)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80001334</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,8 +2062,28 @@
           <t>Ostlänken Norrköpings kommun (OLP2)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80000421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>